--- a/artfynd/A 33353-2024 artfynd.xlsx
+++ b/artfynd/A 33353-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105307087</v>
+        <v>105307098</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541321.2724787275</v>
+        <v>541352</v>
       </c>
       <c r="R2" t="n">
-        <v>6885627.154577455</v>
+        <v>6885634</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,29 +743,40 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>På låga av sälg</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea # På låga av sälg</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,37 +793,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105307092</v>
+        <v>105307086</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>388</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541266.9078632161</v>
+        <v>541307</v>
       </c>
       <c r="R3" t="n">
-        <v>6885816.154029277</v>
+        <v>6885515</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,27 +861,18 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,37 +891,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105307094</v>
+        <v>105307091</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541322.63398214</v>
+        <v>541243</v>
       </c>
       <c r="R4" t="n">
-        <v>6885822.921826146</v>
+        <v>6885812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +959,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +991,7 @@
         <v>105307088</v>
       </c>
       <c r="B5" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541307.1357671404</v>
+        <v>541307</v>
       </c>
       <c r="R5" t="n">
-        <v>6885632.601789689</v>
+        <v>6885633</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1056,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105307099</v>
+        <v>105307090</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1096,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541361.5728284905</v>
+        <v>541188</v>
       </c>
       <c r="R6" t="n">
-        <v>6885591.586322131</v>
+        <v>6885784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1153,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105307095</v>
+        <v>105307089</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1193,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541352.6333354808</v>
+        <v>541177</v>
       </c>
       <c r="R7" t="n">
-        <v>6885747.424545032</v>
+        <v>6885753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1250,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1279,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105307097</v>
+        <v>105307093</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1314,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541383.7538945928</v>
+        <v>541267</v>
       </c>
       <c r="R8" t="n">
-        <v>6885733.755946336</v>
+        <v>6885816</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,28 +1347,17 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1460,15 +1376,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105307098</v>
+        <v>105307094</v>
       </c>
       <c r="B9" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,21 +1387,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541352.1365336676</v>
+        <v>541323</v>
       </c>
       <c r="R9" t="n">
-        <v>6885634.55630876</v>
+        <v>6885823</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,50 +1444,19 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>På låga av sälg</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Salix caprea # På låga av sälg</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,12 +1476,7 @@
         <v>105307096</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1633,10 +1508,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541352.6333354808</v>
+        <v>541353</v>
       </c>
       <c r="R10" t="n">
-        <v>6885747.424545032</v>
+        <v>6885747</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,19 +1541,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,37 +1570,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105307424</v>
+        <v>105307097</v>
       </c>
       <c r="B11" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1745,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541383.7538945928</v>
+        <v>541384</v>
       </c>
       <c r="R11" t="n">
-        <v>6885733.755946336</v>
+        <v>6885734</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,19 +1638,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,15 +1668,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105307093</v>
+        <v>105307099</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,10 +1703,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541266.9078632161</v>
+        <v>541362</v>
       </c>
       <c r="R12" t="n">
-        <v>6885816.154029277</v>
+        <v>6885591</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,19 +1736,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,12 +1768,7 @@
         <v>105307100</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541347.9450642426</v>
+        <v>541348</v>
       </c>
       <c r="R13" t="n">
-        <v>6885555.358850708</v>
+        <v>6885556</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,19 +1833,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,15 +1862,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105307089</v>
+        <v>105307092</v>
       </c>
       <c r="B14" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,21 +1873,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2082,10 +1897,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541177.6289346804</v>
+        <v>541267</v>
       </c>
       <c r="R14" t="n">
-        <v>6885753.251629915</v>
+        <v>6885816</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,19 +1930,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,37 +1959,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105307086</v>
+        <v>105307424</v>
       </c>
       <c r="B15" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>388</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2194,10 +1994,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541307.6324297525</v>
+        <v>541384</v>
       </c>
       <c r="R15" t="n">
-        <v>6885515.058596297</v>
+        <v>6885734</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,19 +2027,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,37 +2057,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105307090</v>
+        <v>105307087</v>
       </c>
       <c r="B16" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,10 +2092,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541188.0379642406</v>
+        <v>541321</v>
       </c>
       <c r="R16" t="n">
-        <v>6885784.285865156</v>
+        <v>6885627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,19 +2125,9 @@
           <t>2022-10-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,6 +2151,103 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>105307095</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Burseklackens sydvästsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>541353</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6885747</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-10-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-10-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Veronica Jägbrant</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33353-2024 artfynd.xlsx
+++ b/artfynd/A 33353-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307098</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307086</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307091</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307088</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307090</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307089</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307093</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1470,6 +1510,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307094</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,6 +1612,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307096</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307097</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1762,6 +1817,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307099</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1859,6 +1919,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307100</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1956,6 +2021,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307092</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2054,6 +2124,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307424</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2151,6 +2226,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307087</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2248,8 +2328,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105307095</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>